--- a/gentrification_risk_index.xlsx
+++ b/gentrification_risk_index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramra\OneDrive\Desktop\Individual Gentrification Project\gentrification-risk-index\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE95F557-03E1-4EE5-B484-EF37C41EC537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098E0F11-66C4-47D0-A1CA-70D443B7227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0B6FBAD5-73A5-4EC5-9B05-79911AEEB115}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{0B6FBAD5-73A5-4EC5-9B05-79911AEEB115}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Journal" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="166">
   <si>
     <t>Step</t>
   </si>
@@ -507,13 +507,37 @@
     <t xml:space="preserve">Also categorized tratcs if they were detirmed to be super early stage or super late stage currently based on the indicators and gave these a 2x multiplier because we can be even more confident about the effects of these </t>
   </si>
   <si>
-    <t>Created a 2023 baseline to add context to what stage of gentrification the tract is currently in before the forecast. For tracts with no 2023 data available it was interpolated.</t>
-  </si>
-  <si>
-    <t>Overhaul Forecast script (create Gentrification baseline index)</t>
-  </si>
-  <si>
     <t>Left 311 calls out of the GBI because their impact on gentrification is dependent on the stage of gentrification so adding them really won't add much value even if I created another glimpse of the top 3 indicators to base it off of like when I forecasted the 311 calls. Also still negate vacancy</t>
+  </si>
+  <si>
+    <t>Create Gentrification baseline index</t>
+  </si>
+  <si>
+    <t>Attempt 3: normalized forecasts into one gentrification score</t>
+  </si>
+  <si>
+    <t>Created a 2023 baseline to add context to what stage of gentrification the tract is currently in before the forecast. For tracts with no 2023 data available it was interpolated. Also will use these interpolated values for the 2024 deltas.</t>
+  </si>
+  <si>
+    <t>After creating the interpolated raw data to create a 2023 baseline it makes sense to use this new data for my 2024 deltas  since there will be less missing data replaced with reasonable interpolations</t>
+  </si>
+  <si>
+    <t>Use interpolated 2023 values for 2024 deltas in normalization scripts</t>
+  </si>
+  <si>
+    <t>Not going to implement it into the forecast scripts because I feel it is generally a fair enough estamite for the deltas but not rigouous enough to impact my forecasts of the raw data</t>
+  </si>
+  <si>
+    <t>Overhaul forecasting scripts again</t>
+  </si>
+  <si>
+    <t>3 year rolling average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewing my work I found another issue, for almost all tracts and all 8 indicators the 2025 and 2026 forecasts were going flat and almost identical across the board. To fix this tried different smoothing methods and decided with </t>
+  </si>
+  <si>
+    <t>Change from rolling average to LOESS because LOESS adapts to local trends without flattening abrupt but valid shifts which was happening in 2026 (the first year the rolling average was being applied)</t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1612,9 @@
       <c r="C27" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -1660,10 +1686,10 @@
         <v>156</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -1671,31 +1697,49 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+    <row r="32" spans="1:9" ht="85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>45827</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+    <row r="33" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>45828</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>

--- a/gentrification_risk_index.xlsx
+++ b/gentrification_risk_index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramra\OneDrive\Desktop\Individual Gentrification Project\gentrification-risk-index\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098E0F11-66C4-47D0-A1CA-70D443B7227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94603F21-C697-4A2B-B9B9-1FDF3B2675C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{0B6FBAD5-73A5-4EC5-9B05-79911AEEB115}"/>
   </bookViews>
@@ -525,9 +525,6 @@
     <t>Use interpolated 2023 values for 2024 deltas in normalization scripts</t>
   </si>
   <si>
-    <t>Not going to implement it into the forecast scripts because I feel it is generally a fair enough estamite for the deltas but not rigouous enough to impact my forecasts of the raw data</t>
-  </si>
-  <si>
     <t>Overhaul forecasting scripts again</t>
   </si>
   <si>
@@ -538,6 +535,9 @@
   </si>
   <si>
     <t>Change from rolling average to LOESS because LOESS adapts to local trends without flattening abrupt but valid shifts which was happening in 2026 (the first year the rolling average was being applied)</t>
+  </si>
+  <si>
+    <t>Not going to implement it into the forecast scripts because it is generally a fair enough estamite for the deltas but not rigouous enough to impact my forecasts of the raw data</t>
   </si>
 </sst>
 </file>
@@ -1613,7 +1613,7 @@
         <v>141</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1708,7 +1708,7 @@
         <v>159</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -1716,18 +1716,18 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="112" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>45828</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -1736,7 +1736,9 @@
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="1"/>
+      <c r="A34" s="2">
+        <v>45830</v>
+      </c>
       <c r="B34" s="1" t="s">
         <v>157</v>
       </c>
